--- a/artfynd/A 20323-2026 artfynd.xlsx
+++ b/artfynd/A 20323-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123435030</v>
+        <v>123321808</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +708,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bysjön, Gstr</t>
+          <t>Bosjön, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613533</v>
+        <v>613653</v>
       </c>
       <c r="R2" t="n">
-        <v>6738750</v>
+        <v>6738759</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2023_110</t>
+          <t>2024_113</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>En sporkapsel</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Oscar Ekberg</t>
+          <t>Pernilla Vesterberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,15 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123435031</v>
+        <v>123435030</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,14 +840,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bosjön, Gstr</t>
+          <t>Bysjön, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613559</v>
+        <v>613533</v>
       </c>
       <c r="R3" t="n">
-        <v>6738816</v>
+        <v>6738750</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +874,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2023_108</t>
+          <t>2023_110</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -928,6 +923,131 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123435031</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bosjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>613559</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6738816</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2023_108</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Oscar Ekberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 20323-2026 artfynd.xlsx
+++ b/artfynd/A 20323-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321808</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123435030</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,8 +1067,18 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123435031</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>